--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="373">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -428,33 +428,220 @@
     <t>FamilyMemberHistory.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Auteur</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension.extension.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:actor.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:actor.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-auteur-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
+</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -462,6 +649,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -545,9 +735,6 @@
     <t>completed</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>A code that identifies the status of the family history record.</t>
   </si>
   <si>
@@ -561,10 +748,6 @@
   </si>
   <si>
     <t>FamilyMemberHistory.dataAbsentReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>subject-unknown | withheld | unable-to-obtain | deferred</t>
@@ -642,10 +825,6 @@
     <t>FamilyMemberHistory.name</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>The family member described</t>
   </si>
   <si>
@@ -862,35 +1041,7 @@
     <t>FamilyMemberHistory.condition.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>FamilyMemberHistory.condition.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>FamilyMemberHistory.condition.extension:bodySite</t>
@@ -909,10 +1060,6 @@
     <t>Extension permettant d'indiquer la localisation anatomique d'une condition dans antécédents familiaux</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>FamilyMemberHistory.condition.extension:interpretation</t>
   </si>
   <si>
@@ -943,159 +1090,6 @@
   </si>
   <si>
     <t>Extension permettant d’indiquer la méthode utilisée : techniques biologiques (ex. : titration, agglutination…), techniques d’imagerie dans les demandes d'examen (ultrasound, tomographie, IRM…), des méthodes de mesure spécifiques, etc.</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
-</t>
-  </si>
-  <si>
-    <t>Auteur</t>
-  </si>
-  <si>
-    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.id</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension.id</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:type.id</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension.extension.id</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:type.extension</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:type.url</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode</t>
-  </si>
-  <si>
-    <t>typeCode</t>
-  </si>
-  <si>
-    <t>Type de participation</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:actor</t>
-  </si>
-  <si>
-    <t>actor</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:actor.id</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:actor.url</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-auteur-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
-</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.url</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension:author.value[x]</t>
-  </si>
-  <si>
-    <t>FamilyMemberHistory.condition.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>FamilyMemberHistory.condition.modifierExtension</t>
@@ -1502,8 +1496,8 @@
   <dimension ref="A1:AN59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="64.26171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.48828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.49609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.72265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2468,7 +2462,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2487,17 +2481,15 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>137</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>77</v>
@@ -2534,16 +2526,14 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>138</v>
@@ -2567,7 +2557,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2578,43 +2568,41 @@
         <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>77</v>
       </c>
@@ -2662,7 +2650,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2671,7 +2659,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -2683,7 +2671,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2691,10 +2679,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2705,7 +2693,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>77</v>
@@ -2714,23 +2702,19 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O11" t="s" s="2">
         <v>150</v>
       </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>77</v>
       </c>
@@ -2778,22 +2762,22 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>77</v>
@@ -2802,12 +2786,12 @@
         <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>154</v>
@@ -2818,7 +2802,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>79</v>
@@ -2830,16 +2814,16 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2878,19 +2862,19 @@
         <v>77</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2902,16 +2886,16 @@
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -2919,21 +2903,23 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -2942,20 +2928,18 @@
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3004,7 +2988,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3016,27 +3000,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3044,32 +3028,30 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3079,7 +3061,7 @@
         <v>77</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>77</v>
@@ -3094,13 +3076,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3118,10 +3100,10 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>88</v>
@@ -3130,27 +3112,27 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>174</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3161,7 +3143,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3170,21 +3152,19 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>179</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3208,43 +3188,43 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
@@ -3253,22 +3233,22 @@
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3278,31 +3258,33 @@
         <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>77</v>
@@ -3344,7 +3326,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3356,27 +3338,27 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3390,29 +3372,25 @@
         <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3421,7 +3399,7 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>77</v>
@@ -3436,13 +3414,11 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>77</v>
@@ -3460,7 +3436,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3481,20 +3457,22 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3512,21 +3490,19 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>201</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
-      <c r="O18" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3574,19 +3550,19 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
@@ -3595,18 +3571,18 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3614,28 +3590,28 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3662,11 +3638,13 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>77</v>
@@ -3684,10 +3662,10 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>88</v>
@@ -3696,7 +3674,7 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
@@ -3705,7 +3683,7 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3713,10 +3691,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3727,7 +3705,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3736,23 +3714,19 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3776,43 +3750,43 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>216</v>
+        <v>77</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3829,10 +3803,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3840,7 +3814,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>88</v>
@@ -3855,24 +3829,24 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>166</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>77</v>
@@ -3914,19 +3888,19 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3935,7 +3909,7 @@
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3943,10 +3917,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3966,23 +3940,19 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4030,7 +4000,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4039,7 +4009,7 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>100</v>
@@ -4051,7 +4021,7 @@
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4059,18 +4029,20 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>88</v>
@@ -4082,29 +4054,23 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>134</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q23" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4148,19 +4114,19 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>157</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
@@ -4177,10 +4143,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4200,16 +4166,16 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>148</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>149</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>150</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4260,7 +4226,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4272,7 +4238,7 @@
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
@@ -4281,7 +4247,7 @@
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>245</v>
+        <v>152</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4289,10 +4255,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4303,7 +4269,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4312,20 +4278,18 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>134</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4350,31 +4314,31 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>250</v>
+        <v>77</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4386,27 +4350,27 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>190</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>165</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4414,10 +4378,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4426,25 +4390,27 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>166</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>77</v>
@@ -4486,39 +4452,39 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>169</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>257</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>191</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>171</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4529,7 +4495,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4541,13 +4507,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>172</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4598,13 +4564,13 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>177</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
@@ -4613,24 +4579,24 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>131</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>193</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>194</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4638,13 +4604,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>77</v>
@@ -4653,22 +4619,24 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>266</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>166</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>77</v>
@@ -4710,19 +4678,19 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>169</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
@@ -4731,7 +4699,7 @@
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>269</v>
+        <v>131</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4739,10 +4707,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>196</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4753,7 +4721,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4765,13 +4733,13 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>172</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>173</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4822,7 +4790,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>273</v>
+        <v>177</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4834,7 +4802,7 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
@@ -4843,7 +4811,7 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>274</v>
+        <v>131</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4851,14 +4819,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4871,22 +4839,26 @@
         <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>201</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -4922,17 +4894,19 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>205</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4953,22 +4927,20 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>206</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>77</v>
       </c>
@@ -4977,28 +4949,32 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K31" t="s" s="2">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5046,7 +5022,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5055,34 +5031,32 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5091,25 +5065,25 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K32" t="s" s="2">
-        <v>289</v>
+        <v>216</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>291</v>
+        <v>218</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5160,7 +5134,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>215</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5169,34 +5143,32 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5205,27 +5177,29 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>294</v>
+        <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>222</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5274,7 +5248,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>280</v>
+        <v>221</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5283,19 +5257,19 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5303,20 +5277,18 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>226</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
@@ -5325,21 +5297,23 @@
         <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>299</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>227</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5349,7 +5323,7 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>77</v>
@@ -5364,13 +5338,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5388,22 +5362,22 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
@@ -5412,15 +5386,15 @@
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5440,19 +5414,21 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5476,13 +5452,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>77</v>
+        <v>241</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5500,7 +5476,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5512,7 +5488,7 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5521,47 +5497,47 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>243</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>243</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>306</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>134</v>
+        <v>245</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5600,85 +5576,87 @@
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>77</v>
+        <v>249</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>134</v>
+        <v>252</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5726,19 +5704,19 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
@@ -5747,18 +5725,18 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>77</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>259</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5778,19 +5756,21 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -5838,7 +5818,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5850,7 +5830,7 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -5859,18 +5839,18 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5878,28 +5858,28 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5926,43 +5906,41 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -5971,7 +5949,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -5979,10 +5957,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>269</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>269</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5990,7 +5968,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
@@ -6002,27 +5980,29 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>316</v>
+        <v>270</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>317</v>
+        <v>271</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>77</v>
@@ -6040,13 +6020,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6064,10 +6044,10 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>88</v>
@@ -6076,7 +6056,7 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -6085,7 +6065,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6093,10 +6073,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>277</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6119,16 +6099,18 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>108</v>
+        <v>278</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6137,7 +6119,7 @@
         <v>77</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>77</v>
@@ -6152,11 +6134,13 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>325</v>
+        <v>77</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6174,7 +6158,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6183,7 +6167,7 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
@@ -6195,7 +6179,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6203,14 +6187,12 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6228,19 +6210,23 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>285</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6288,19 +6274,19 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6309,7 +6295,7 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6317,10 +6303,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6340,23 +6326,29 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>201</v>
+        <v>292</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q43" s="2"/>
+      <c r="Q43" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="R43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6400,7 +6392,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6409,10 +6401,10 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6421,7 +6413,7 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>274</v>
+        <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6429,10 +6421,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6443,7 +6435,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6452,16 +6444,16 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>134</v>
+        <v>300</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6500,31 +6492,31 @@
         <v>77</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
@@ -6533,7 +6525,7 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6541,10 +6533,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6552,10 +6544,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6564,19 +6556,19 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6584,7 +6576,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>77</v>
@@ -6602,13 +6594,13 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>77</v>
+        <v>308</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6626,39 +6618,39 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>77</v>
+        <v>310</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>131</v>
+        <v>242</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6669,7 +6661,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6678,16 +6670,16 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>176</v>
+        <v>313</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6738,13 +6730,13 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
@@ -6753,37 +6745,35 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>77</v>
+        <v>315</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>131</v>
+        <v>316</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6795,13 +6785,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>318</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>276</v>
+        <v>319</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>277</v>
+        <v>320</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6852,7 +6842,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6864,27 +6854,27 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>77</v>
+        <v>321</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>77</v>
+        <v>322</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6895,10 +6885,10 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>77</v>
@@ -6907,13 +6897,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>201</v>
+        <v>324</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>271</v>
+        <v>325</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6964,19 +6954,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -6985,7 +6975,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -6993,10 +6983,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7007,7 +6997,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7019,13 +7009,13 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>276</v>
+        <v>149</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>277</v>
+        <v>150</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7064,31 +7054,31 @@
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>280</v>
+        <v>151</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7097,7 +7087,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7105,10 +7095,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7116,10 +7106,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7131,24 +7121,22 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>316</v>
+        <v>134</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>77</v>
@@ -7178,31 +7166,29 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>319</v>
+        <v>157</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7211,20 +7197,22 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7236,7 +7224,7 @@
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
@@ -7245,13 +7233,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7302,19 +7290,19 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>326</v>
+        <v>157</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
@@ -7323,32 +7311,34 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>77</v>
@@ -7357,24 +7347,22 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>337</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>343</v>
+        <v>77</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>77</v>
@@ -7416,19 +7404,19 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>319</v>
+        <v>157</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7437,20 +7425,22 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7459,10 +7449,10 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>77</v>
@@ -7471,13 +7461,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7528,19 +7518,19 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>326</v>
+        <v>157</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7549,7 +7539,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7557,14 +7547,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7583,19 +7573,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7644,7 +7634,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7673,10 +7663,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7699,13 +7689,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7732,11 +7722,11 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7754,7 +7744,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>88</v>
@@ -7775,7 +7765,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7783,10 +7773,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7809,13 +7799,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7842,13 +7832,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>180</v>
+        <v>239</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -7866,7 +7856,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7887,7 +7877,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -7895,10 +7885,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7921,13 +7911,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7978,7 +7968,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8007,10 +7997,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8033,17 +8023,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8092,7 +8082,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8113,7 +8103,7 @@
         <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8121,10 +8111,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8147,13 +8137,13 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8204,7 +8194,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8225,7 +8215,7 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/main/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
